--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 DEER BUCK GENERAL SEASON - PRIVATE LAND ONLY ANY LEGAL WEAPON.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 DEER BUCK GENERAL SEASON - PRIVATE LAND ONLY ANY LEGAL WEAPON.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -645,7 +650,8 @@
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -706,7 +712,8 @@
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -771,7 +778,8 @@
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
@@ -836,7 +844,8 @@
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -893,7 +902,8 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -942,7 +952,8 @@
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -995,7 +1006,8 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1060,7 +1072,8 @@
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1125,7 +1138,8 @@
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
@@ -1178,7 +1192,8 @@
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1239,7 +1254,8 @@
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -1300,7 +1316,8 @@
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -1365,7 +1382,8 @@
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1422,7 +1440,8 @@
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1479,7 +1498,8 @@
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1540,7 +1560,8 @@
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
@@ -1601,7 +1622,8 @@
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -1662,7 +1684,8 @@
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1723,7 +1746,8 @@
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -1784,7 +1808,8 @@
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1849,7 +1874,8 @@
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -1914,7 +1940,8 @@
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1971,7 +1998,8 @@
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -2032,7 +2060,8 @@
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
@@ -2093,7 +2122,8 @@
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2150,7 +2180,8 @@
       <c r="L27" s="3" t="inlineStr"/>
       <c r="M27" s="3" t="inlineStr"/>
       <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -2203,7 +2234,8 @@
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -2264,7 +2296,8 @@
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -2317,7 +2350,8 @@
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2378,7 +2412,8 @@
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -2431,7 +2466,8 @@
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2492,7 +2528,8 @@
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -2545,7 +2582,8 @@
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -2594,7 +2632,8 @@
       <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="3" t="inlineStr"/>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2647,7 +2686,8 @@
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -2696,7 +2736,8 @@
       <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
